--- a/survey_templates/015_much_ado_about_nothing_quiz--survey_templates.xlsx
+++ b/survey_templates/015_much_ado_about_nothing_quiz--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1098,7 +1098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C25"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="49" customWidth="1" min="1" max="1"/>
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'text':_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'text': 'option_1'}</t>
+          <t>option 1</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'text':_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'text': 'option_2'}</t>
+          <t>option 2</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'text':_'option_3'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'text': 'option_3'}</t>
+          <t>option 3</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'text':_'option_4'}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'text': 'option_4'}</t>
+          <t>option 4</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'text':_'option_5'}</t>
+          <t>option_5</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'text': 'option_5'}</t>
+          <t>option 5</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'text':_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'text': 'option_1'}</t>
+          <t>option 1</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'text':_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'text': 'option_2'}</t>
+          <t>option 2</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'text':_'option_3'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'text': 'option_3'}</t>
+          <t>option 3</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'text':_'option_4'}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'text': 'option_4'}</t>
+          <t>option 4</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'text':_'option_5'}</t>
+          <t>option_5</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'text': 'option_5'}</t>
+          <t>option 5</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'text':_'survey_templates'}</t>
+          <t>survey_templates</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'text': 'survey_templates'}</t>
+          <t>survey templates</t>
         </is>
       </c>
     </row>
@@ -1318,29 +1318,29 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'text':_'quizzes'}</t>
+          <t>quizzes</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'text': 'quizzes'}</t>
+          <t>quizzes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>much_ado_about_nothing_quiz_category_choices</t>
+          <t>much_ado_about_nothing_quiz_category_2_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'text':_'quizzes'}</t>
+          <t>survey_templates</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'text': 'quizzes'}</t>
+          <t>survey templates</t>
         </is>
       </c>
     </row>
@@ -1352,182 +1352,114 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'text':_'survey_templates'}</t>
+          <t>quizzes</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'text': 'survey_templates'}</t>
+          <t>quizzes</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>much_ado_about_nothing_quiz_category_2_choices</t>
+          <t>much_ado_about_nothing_quiz_category_3_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'text':_'quizzes'}</t>
+          <t>survey_templates</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'text': 'quizzes'}</t>
+          <t>survey templates</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>much_ado_about_nothing_quiz_category_2_choices</t>
+          <t>much_ado_about_nothing_quiz_category_3_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'text':_'quizzes'}</t>
+          <t>quizzes</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'text': 'quizzes'}</t>
+          <t>quizzes</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>much_ado_about_nothing_quiz_category_3_choices</t>
+          <t>much_ado_about_nothing_quiz_category_4_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'text':_'survey_templates'}</t>
+          <t>survey_templates</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'text': 'survey_templates'}</t>
+          <t>survey templates</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>much_ado_about_nothing_quiz_category_3_choices</t>
+          <t>much_ado_about_nothing_quiz_category_4_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'text':_'quizzes'}</t>
+          <t>quizzes</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'text': 'quizzes'}</t>
+          <t>quizzes</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>much_ado_about_nothing_quiz_category_3_choices</t>
+          <t>much_ado_about_nothing_quiz_output_file_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'text':_'quizzes'}</t>
+          <t>015_much_ado_about_nothing_quiz--survey_templates.yaml</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'text': 'quizzes'}</t>
+          <t>015 much ado about nothing quiz--survey templates.yaml</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>much_ado_about_nothing_quiz_category_4_choices</t>
+          <t>much_ado_about_nothing_quiz_output_file_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'text':_'survey_templates'}</t>
+          <t>015_much_ado_about_nothing_quiz--quizzes.yaml</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'text': 'survey_templates'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>much_ado_about_nothing_quiz_category_4_choices</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>{'text':_'quizzes'}</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>{'text': 'quizzes'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>much_ado_about_nothing_quiz_category_4_choices</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>{'text':_'quizzes'}</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>{'text': 'quizzes'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>much_ado_about_nothing_quiz_output_file_choices</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>{'text':_'015_much_ado_about_nothing_quiz--survey_templates.yaml'}</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>{'text': '015_much_ado_about_nothing_quiz--survey_templates.yaml'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>much_ado_about_nothing_quiz_output_file_choices</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>{'text':_'015_much_ado_about_nothing_quiz--quizzes.yaml'}</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>{'text': '015_much_ado_about_nothing_quiz--quizzes.yaml'}</t>
+          <t>015 much ado about nothing quiz--quizzes.yaml</t>
         </is>
       </c>
     </row>
